--- a/artfynd/A 32218-2023 artfynd.xlsx
+++ b/artfynd/A 32218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1718,6 +1718,116 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124689937</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Helgum, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590482</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7007003</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32218-2023 artfynd.xlsx
+++ b/artfynd/A 32218-2023 artfynd.xlsx
@@ -1723,7 +1723,7 @@
         <v>124689937</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 32218-2023 artfynd.xlsx
+++ b/artfynd/A 32218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115429512</v>
+        <v>116882889</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590486</v>
+        <v>590378</v>
       </c>
       <c r="R2" t="n">
-        <v>7006924</v>
+        <v>7006953</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115429522</v>
+        <v>115429481</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590414</v>
+        <v>590380</v>
       </c>
       <c r="R3" t="n">
-        <v>7007012</v>
+        <v>7006919</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,55 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115429730</v>
+        <v>115429522</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590441</v>
+        <v>590414</v>
       </c>
       <c r="R4" t="n">
-        <v>7006948</v>
+        <v>7007012</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115429492</v>
+        <v>7130829</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,27 +977,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1031,13 +1005,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590437</v>
+        <v>590522</v>
       </c>
       <c r="R5" t="n">
-        <v>7006961</v>
+        <v>7007030</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2013-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,27 +1055,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Askia Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Askia Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115429493</v>
+        <v>115429505</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,39 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590428</v>
+        <v>590438</v>
       </c>
       <c r="R6" t="n">
-        <v>7006960</v>
+        <v>7006876</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1200,15 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115429731</v>
+        <v>115429510</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,39 +1179,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590386</v>
+        <v>590499</v>
       </c>
       <c r="R7" t="n">
-        <v>7006937</v>
+        <v>7007001</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1295,27 +1253,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115429510</v>
+        <v>115429511</v>
       </c>
       <c r="B8" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590499</v>
+        <v>590483</v>
       </c>
       <c r="R8" t="n">
-        <v>7007001</v>
+        <v>7006925</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1409,15 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115429481</v>
+        <v>115429512</v>
       </c>
       <c r="B9" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,21 +1373,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590380</v>
+        <v>590486</v>
       </c>
       <c r="R9" t="n">
-        <v>7006919</v>
+        <v>7006924</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1511,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115429494</v>
+        <v>115429490</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590407</v>
+        <v>590358</v>
       </c>
       <c r="R10" t="n">
-        <v>7007016</v>
+        <v>7006934</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1618,15 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115429511</v>
+        <v>115429491</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1572,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590483</v>
+        <v>590528</v>
       </c>
       <c r="R11" t="n">
-        <v>7006925</v>
+        <v>7007013</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1720,15 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124689937</v>
+        <v>115429492</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,27 +1692,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Helgum, Ång</t>
+          <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590482</v>
+        <v>590437</v>
       </c>
       <c r="R12" t="n">
-        <v>7007003</v>
+        <v>7006961</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1798,12 +1733,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,15 +1753,630 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115429493</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590428</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7006960</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115429494</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590407</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7007016</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115429730</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>590441</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7006948</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115429731</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>590386</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7006937</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124689937</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Helgum, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590482</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7007003</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Fatima Boukarchid</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Fatima Boukarchid</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>116882931</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590418</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7007005</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32218-2023 artfynd.xlsx
+++ b/artfynd/A 32218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116882889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429481</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7130829</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429511</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429491</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429492</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429493</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429494</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429730</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429731</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2275,6 +2355,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689937</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,8 +2462,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116882931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>